--- a/Java24_CongKhoa_DatabaseDesign.xlsx
+++ b/Java24_CongKhoa_DatabaseDesign.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\khoanc\java24\3. Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC1C5B2-5A06-4EBF-8292-C2AF28B0B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D038B72-E065-44E8-A78F-76672E2C285E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10980" yWindow="360" windowWidth="11292" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Mathang</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>MaMH</t>
   </si>
@@ -52,13 +49,142 @@
   </si>
   <si>
     <t>MauSac(s)</t>
+  </si>
+  <si>
+    <t>HinhAnh(s)</t>
+  </si>
+  <si>
+    <t>MatHang</t>
+  </si>
+  <si>
+    <t>MaLMH</t>
+  </si>
+  <si>
+    <t>TenLMH</t>
+  </si>
+  <si>
+    <t>MatHang (MaMH)</t>
+  </si>
+  <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
+    <t>KhachHang</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>SoDienThoai</t>
+  </si>
+  <si>
+    <t>GioiTinh</t>
+  </si>
+  <si>
+    <t>NgaySinh</t>
+  </si>
+  <si>
+    <t>DiaChi</t>
+  </si>
+  <si>
+    <t>TaiKhoan</t>
+  </si>
+  <si>
+    <t>TrangThai</t>
+  </si>
+  <si>
+    <t>NhanVien</t>
+  </si>
+  <si>
+    <t>ChucVu (KH, NV, Admin)</t>
+  </si>
+  <si>
+    <t>DonHang</t>
+  </si>
+  <si>
+    <t>MaKH</t>
+  </si>
+  <si>
+    <t>TenKH</t>
+  </si>
+  <si>
+    <t>MaNV</t>
+  </si>
+  <si>
+    <t>TenNV</t>
+  </si>
+  <si>
+    <t>MaTK</t>
+  </si>
+  <si>
+    <t>TenTK</t>
+  </si>
+  <si>
+    <t>MatKhauTK</t>
+  </si>
+  <si>
+    <t>TrangThaiTK</t>
+  </si>
+  <si>
+    <t>MaDH</t>
+  </si>
+  <si>
+    <t>KhachHang (MaKH)</t>
+  </si>
+  <si>
+    <t>TaiKhoan (MaTK)</t>
+  </si>
+  <si>
+    <t>NgayDatHang</t>
+  </si>
+  <si>
+    <t>DiaChiGiaoHang</t>
+  </si>
+  <si>
+    <t>TrangThaiĐH</t>
+  </si>
+  <si>
+    <t>NhanVien (MaNV)</t>
+  </si>
+  <si>
+    <t>ChiTietDonHang</t>
+  </si>
+  <si>
+    <t>MaChiTietDH</t>
+  </si>
+  <si>
+    <t>DonHang (MaDH)</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>LoaiHinhThanhToan</t>
+  </si>
+  <si>
+    <t>MauSac</t>
+  </si>
+  <si>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>ThongKe</t>
+  </si>
+  <si>
+    <t>MaHang (MaMH)</t>
+  </si>
+  <si>
+    <t>TonKho</t>
+  </si>
+  <si>
+    <t>ChiTietDH(MaChiTietDH)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +193,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -115,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -127,6 +261,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -412,7 +549,8 @@
   <dimension ref="A1:X24"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="24" width="17.33203125" style="1" customWidth="1"/>
+    <col min="1" max="22" width="23.21875" style="1" customWidth="1"/>
+    <col min="23" max="24" width="17.33203125" style="1" customWidth="1"/>
     <col min="25" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -422,15 +560,29 @@
     <row r="4" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -438,15 +590,29 @@
     </row>
     <row r="6" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -454,15 +620,29 @@
     </row>
     <row r="7" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -470,15 +650,29 @@
     </row>
     <row r="8" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -486,14 +680,24 @@
     </row>
     <row r="9" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -502,14 +706,24 @@
     </row>
     <row r="10" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -518,14 +732,22 @@
     </row>
     <row r="11" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -534,13 +756,19 @@
     </row>
     <row r="12" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -550,13 +778,19 @@
     </row>
     <row r="13" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="D13" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="F13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -565,7 +799,9 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="4"/>
+      <c r="B14" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -579,7 +815,9 @@
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -593,7 +831,9 @@
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -606,14 +846,53 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
